--- a/artfynd/A 53436-2025 artfynd.xlsx
+++ b/artfynd/A 53436-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>94094595</v>
       </c>
       <c r="B2" t="n">
-        <v>77590</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79408</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388561.1880530422</v>
+        <v>388561</v>
       </c>
       <c r="R2" t="n">
-        <v>7062155.864276942</v>
+        <v>7062156</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -787,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94094594</v>
+        <v>94226944</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79408</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388230.444050303</v>
+        <v>388855</v>
       </c>
       <c r="R3" t="n">
-        <v>7062125.77275893</v>
+        <v>7062218</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-06-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:59</t>
+          <t>2021-06-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-06-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:59</t>
+          <t>2021-06-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,31 +863,41 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>94094596</v>
+        <v>94094597</v>
       </c>
       <c r="B4" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1467</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>388843.6300997972</v>
+        <v>388843</v>
       </c>
       <c r="R4" t="n">
-        <v>7062191.686187825</v>
+        <v>7062191</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1011,53 +1001,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>94094597</v>
+        <v>520752</v>
       </c>
       <c r="B5" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>308</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Seglan, Jmt</t>
+          <t>(20C3j01), Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>388843.6300997972</v>
+        <v>388829</v>
       </c>
       <c r="R5" t="n">
-        <v>7062191.686187825</v>
+        <v>7062027</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1066,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-06-05</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>19:49</t>
+          <t>1996-07-31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-06-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>19:49</t>
+          <t>1996-07-31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>200239011 / PHE NIGL / Allmän-riklig (3)  / OBJ.AREA:1,2 ha</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,69 +1087,78 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Barrskog /</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Låga av gran</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Stina Osterman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>94094598</v>
+        <v>352927</v>
       </c>
       <c r="B6" t="n">
-        <v>78533</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229748</v>
+        <v>1249</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Seglan, Jmt</t>
+          <t>(20C3j01), Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>388847.302232959</v>
+        <v>388829</v>
       </c>
       <c r="R6" t="n">
-        <v>7062207.552327489</v>
+        <v>7062027</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,22 +1182,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-06-05</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>19:32</t>
+          <t>1996-07-31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-06-05</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>19:32</t>
+          <t>1996-07-31</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>200239011 / PLA NORV / Ej bedömd (0)  / OBJ.AREA:1,2 ha</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,31 +1203,35 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Barrskog /</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Stina Osterman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>94226944</v>
+        <v>94094596</v>
       </c>
       <c r="B7" t="n">
-        <v>77590</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1239,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>283</v>
+        <v>1467</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,13 +1263,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>388855.2618157982</v>
+        <v>388843</v>
       </c>
       <c r="R7" t="n">
-        <v>7062218.824567253</v>
+        <v>7062191</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,7 +1298,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1308,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,34 +1319,242 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6454496</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>(20C3j01), Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>388829</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7062027</v>
+      </c>
+      <c r="S8" t="n">
+        <v>100</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>1996-07-31</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>1996-07-31</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>200239011 / PAR TRIP / Ej bedömd (0)  / OBJ.AREA:1,2 ha</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Barrskog /</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Gammal grov asp</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Stina Osterman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>94094598</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Seglan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>388847</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7062208</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-06-05</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-06-05</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53436-2025 artfynd.xlsx
+++ b/artfynd/A 53436-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94094595</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94226944</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94094597</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1114,6 +1134,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/520752</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1225,6 +1250,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/352927</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1332,6 +1362,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94094596</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1448,6 +1483,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6454496</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1555,8 +1595,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94094598</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>